--- a/artfynd/A 55422-2024 artfynd.xlsx
+++ b/artfynd/A 55422-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123805063</v>
+        <v>123802394</v>
       </c>
       <c r="B2" t="n">
-        <v>91003</v>
+        <v>90988</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573734</v>
+        <v>573646</v>
       </c>
       <c r="R2" t="n">
-        <v>7056784</v>
+        <v>7056941</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123801614</v>
+        <v>123802294</v>
       </c>
       <c r="B3" t="n">
-        <v>56689</v>
+        <v>91275</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bergmyran, Bergmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573694</v>
+        <v>573643</v>
       </c>
       <c r="R3" t="n">
-        <v>7056860</v>
+        <v>7056933</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123802574</v>
+        <v>123802645</v>
       </c>
       <c r="B4" t="n">
-        <v>79862</v>
+        <v>57506</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,34 +915,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bergmyran, Bergmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573619</v>
+        <v>573634</v>
       </c>
       <c r="R4" t="n">
-        <v>7056981</v>
+        <v>7056989</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123802394</v>
+        <v>123802226</v>
       </c>
       <c r="B5" t="n">
-        <v>90983</v>
+        <v>78786</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,21 +1032,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>573646</v>
+        <v>573653</v>
       </c>
       <c r="R5" t="n">
-        <v>7056941</v>
+        <v>7056943</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123802226</v>
+        <v>123801614</v>
       </c>
       <c r="B6" t="n">
-        <v>78781</v>
+        <v>56692</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,34 +1144,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bergmyran, Bergmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>573653</v>
+        <v>573694</v>
       </c>
       <c r="R6" t="n">
-        <v>7056943</v>
+        <v>7056860</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123802645</v>
+        <v>123805063</v>
       </c>
       <c r="B7" t="n">
-        <v>57503</v>
+        <v>91008</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,39 +1261,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bergmyran, Bergmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>573634</v>
+        <v>573734</v>
       </c>
       <c r="R7" t="n">
-        <v>7056989</v>
+        <v>7056784</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123802294</v>
+        <v>123802574</v>
       </c>
       <c r="B8" t="n">
-        <v>91270</v>
+        <v>79867</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,21 +1373,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>573643</v>
+        <v>573619</v>
       </c>
       <c r="R8" t="n">
-        <v>7056933</v>
+        <v>7056981</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 55422-2024 artfynd.xlsx
+++ b/artfynd/A 55422-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>123802394</v>
       </c>
       <c r="B2" t="n">
-        <v>90988</v>
+        <v>90990</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123802294</v>
+        <v>123805063</v>
       </c>
       <c r="B3" t="n">
-        <v>91275</v>
+        <v>91010</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573643</v>
+        <v>573734</v>
       </c>
       <c r="R3" t="n">
-        <v>7056933</v>
+        <v>7056784</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123802645</v>
+        <v>123801614</v>
       </c>
       <c r="B4" t="n">
-        <v>57506</v>
+        <v>56692</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,16 +915,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -935,7 +935,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573634</v>
+        <v>573694</v>
       </c>
       <c r="R4" t="n">
-        <v>7056989</v>
+        <v>7056860</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123802226</v>
+        <v>123802294</v>
       </c>
       <c r="B5" t="n">
-        <v>78786</v>
+        <v>91277</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,21 +1032,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>573653</v>
+        <v>573643</v>
       </c>
       <c r="R5" t="n">
-        <v>7056943</v>
+        <v>7056933</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123801614</v>
+        <v>123802226</v>
       </c>
       <c r="B6" t="n">
-        <v>56692</v>
+        <v>78788</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,39 +1144,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bergmyran, Bergmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>573694</v>
+        <v>573653</v>
       </c>
       <c r="R6" t="n">
-        <v>7056860</v>
+        <v>7056943</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123805063</v>
+        <v>123802574</v>
       </c>
       <c r="B7" t="n">
-        <v>91008</v>
+        <v>79869</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,21 +1256,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>573734</v>
+        <v>573619</v>
       </c>
       <c r="R7" t="n">
-        <v>7056784</v>
+        <v>7056981</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123802574</v>
+        <v>123802645</v>
       </c>
       <c r="B8" t="n">
-        <v>79867</v>
+        <v>57507</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,34 +1368,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bergmyran, Bergmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>573619</v>
+        <v>573634</v>
       </c>
       <c r="R8" t="n">
-        <v>7056981</v>
+        <v>7056989</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 55422-2024 artfynd.xlsx
+++ b/artfynd/A 55422-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123805063</v>
+        <v>123801614</v>
       </c>
       <c r="B3" t="n">
-        <v>91010</v>
+        <v>56692</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bergmyran, Bergmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573734</v>
+        <v>573694</v>
       </c>
       <c r="R3" t="n">
-        <v>7056784</v>
+        <v>7056860</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123801614</v>
+        <v>123805063</v>
       </c>
       <c r="B4" t="n">
-        <v>56692</v>
+        <v>91010</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,39 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bergmyran, Bergmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573694</v>
+        <v>573734</v>
       </c>
       <c r="R4" t="n">
-        <v>7056860</v>
+        <v>7056784</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 55422-2024 artfynd.xlsx
+++ b/artfynd/A 55422-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123801614</v>
+        <v>123805063</v>
       </c>
       <c r="B3" t="n">
-        <v>56692</v>
+        <v>91010</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>5442</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bergmyran, Bergmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573694</v>
+        <v>573734</v>
       </c>
       <c r="R3" t="n">
-        <v>7056860</v>
+        <v>7056784</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123805063</v>
+        <v>123801614</v>
       </c>
       <c r="B4" t="n">
-        <v>91010</v>
+        <v>56692</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,34 +915,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>102612</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bergmyran, Bergmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573734</v>
+        <v>573694</v>
       </c>
       <c r="R4" t="n">
-        <v>7056784</v>
+        <v>7056860</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 55422-2024 artfynd.xlsx
+++ b/artfynd/A 55422-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123802394</v>
+        <v>123802645</v>
       </c>
       <c r="B2" t="n">
-        <v>90990</v>
+        <v>57507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bergmyran, Bergmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573646</v>
+        <v>573634</v>
       </c>
       <c r="R2" t="n">
-        <v>7056941</v>
+        <v>7056989</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +792,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123805063</v>
+        <v>123802394</v>
       </c>
       <c r="B3" t="n">
-        <v>91010</v>
+        <v>90990</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +808,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573734</v>
+        <v>573646</v>
       </c>
       <c r="R3" t="n">
-        <v>7056784</v>
+        <v>7056941</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123801614</v>
+        <v>123802226</v>
       </c>
       <c r="B4" t="n">
-        <v>56692</v>
+        <v>78788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,39 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bergmyran, Bergmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573694</v>
+        <v>573653</v>
       </c>
       <c r="R4" t="n">
-        <v>7056860</v>
+        <v>7056943</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123802226</v>
+        <v>123802574</v>
       </c>
       <c r="B6" t="n">
-        <v>78788</v>
+        <v>79869</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,21 +1144,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>573653</v>
+        <v>573619</v>
       </c>
       <c r="R6" t="n">
-        <v>7056943</v>
+        <v>7056981</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123802574</v>
+        <v>123801614</v>
       </c>
       <c r="B7" t="n">
-        <v>79869</v>
+        <v>56692</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,34 +1256,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bergmyran, Bergmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>573619</v>
+        <v>573694</v>
       </c>
       <c r="R7" t="n">
-        <v>7056981</v>
+        <v>7056860</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123802645</v>
+        <v>123805063</v>
       </c>
       <c r="B8" t="n">
-        <v>57507</v>
+        <v>91010</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1368,39 +1373,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bergmyran, Bergmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>573634</v>
+        <v>573734</v>
       </c>
       <c r="R8" t="n">
-        <v>7056989</v>
+        <v>7056784</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 55422-2024 artfynd.xlsx
+++ b/artfynd/A 55422-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123802645</v>
+        <v>123802294</v>
       </c>
       <c r="B2" t="n">
-        <v>57507</v>
+        <v>91277</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Bergmyran, Bergmyran, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573634</v>
+        <v>573643</v>
       </c>
       <c r="R2" t="n">
-        <v>7056989</v>
+        <v>7056933</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123802394</v>
+        <v>123801614</v>
       </c>
       <c r="B3" t="n">
-        <v>90990</v>
+        <v>56692</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bergmyran, Bergmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573646</v>
+        <v>573694</v>
       </c>
       <c r="R3" t="n">
-        <v>7056941</v>
+        <v>7056860</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123802294</v>
+        <v>123802394</v>
       </c>
       <c r="B5" t="n">
-        <v>91277</v>
+        <v>90990</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,21 +1032,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1056,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>573643</v>
+        <v>573646</v>
       </c>
       <c r="R5" t="n">
-        <v>7056933</v>
+        <v>7056941</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123802574</v>
+        <v>123805063</v>
       </c>
       <c r="B6" t="n">
-        <v>79869</v>
+        <v>91010</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,21 +1144,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>5442</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>573619</v>
+        <v>573734</v>
       </c>
       <c r="R6" t="n">
-        <v>7056981</v>
+        <v>7056784</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123801614</v>
+        <v>123802645</v>
       </c>
       <c r="B7" t="n">
-        <v>56692</v>
+        <v>57507</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,16 +1256,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1276,7 +1276,7 @@
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1285,10 +1285,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>573694</v>
+        <v>573634</v>
       </c>
       <c r="R7" t="n">
-        <v>7056860</v>
+        <v>7056989</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123805063</v>
+        <v>123802574</v>
       </c>
       <c r="B8" t="n">
-        <v>91010</v>
+        <v>79869</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,21 +1373,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>573734</v>
+        <v>573619</v>
       </c>
       <c r="R8" t="n">
-        <v>7056784</v>
+        <v>7056981</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 55422-2024 artfynd.xlsx
+++ b/artfynd/A 55422-2024 artfynd.xlsx
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123802226</v>
+        <v>123805063</v>
       </c>
       <c r="B4" t="n">
-        <v>78788</v>
+        <v>91010</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,21 +920,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573653</v>
+        <v>573734</v>
       </c>
       <c r="R4" t="n">
-        <v>7056943</v>
+        <v>7056784</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123805063</v>
+        <v>123802226</v>
       </c>
       <c r="B6" t="n">
-        <v>91010</v>
+        <v>78788</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,21 +1144,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1168,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>573734</v>
+        <v>573653</v>
       </c>
       <c r="R6" t="n">
-        <v>7056784</v>
+        <v>7056943</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 55422-2024 artfynd.xlsx
+++ b/artfynd/A 55422-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123802294</v>
+        <v>123802574</v>
       </c>
       <c r="B2" t="n">
-        <v>91277</v>
+        <v>79869</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573643</v>
+        <v>573619</v>
       </c>
       <c r="R2" t="n">
-        <v>7056933</v>
+        <v>7056981</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123801614</v>
+        <v>123802645</v>
       </c>
       <c r="B3" t="n">
-        <v>56692</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,16 +803,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -823,7 +823,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573694</v>
+        <v>573634</v>
       </c>
       <c r="R3" t="n">
-        <v>7056860</v>
+        <v>7056989</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123805063</v>
+        <v>123802226</v>
       </c>
       <c r="B4" t="n">
-        <v>91010</v>
+        <v>78788</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,21 +920,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573734</v>
+        <v>573653</v>
       </c>
       <c r="R4" t="n">
-        <v>7056784</v>
+        <v>7056943</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123802394</v>
+        <v>123801614</v>
       </c>
       <c r="B5" t="n">
-        <v>90990</v>
+        <v>56692</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,34 +1032,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bergmyran, Bergmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>573646</v>
+        <v>573694</v>
       </c>
       <c r="R5" t="n">
-        <v>7056941</v>
+        <v>7056860</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1096,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1106,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1133,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123802226</v>
+        <v>123802394</v>
       </c>
       <c r="B6" t="n">
-        <v>78788</v>
+        <v>90990</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,21 +1149,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>573653</v>
+        <v>573646</v>
       </c>
       <c r="R6" t="n">
-        <v>7056943</v>
+        <v>7056941</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123802645</v>
+        <v>123802294</v>
       </c>
       <c r="B7" t="n">
-        <v>57507</v>
+        <v>91277</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,39 +1261,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bergmyran, Bergmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>573634</v>
+        <v>573643</v>
       </c>
       <c r="R7" t="n">
-        <v>7056989</v>
+        <v>7056933</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123802574</v>
+        <v>123805063</v>
       </c>
       <c r="B8" t="n">
-        <v>79869</v>
+        <v>91010</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,21 +1373,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>5442</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>573619</v>
+        <v>573734</v>
       </c>
       <c r="R8" t="n">
-        <v>7056981</v>
+        <v>7056784</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 55422-2024 artfynd.xlsx
+++ b/artfynd/A 55422-2024 artfynd.xlsx
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123802645</v>
+        <v>123802226</v>
       </c>
       <c r="B3" t="n">
-        <v>57507</v>
+        <v>78788</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Bergmyran, Bergmyran, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573634</v>
+        <v>573653</v>
       </c>
       <c r="R3" t="n">
-        <v>7056989</v>
+        <v>7056943</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123802226</v>
+        <v>123802645</v>
       </c>
       <c r="B4" t="n">
-        <v>78788</v>
+        <v>57507</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,34 +915,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bergmyran, Bergmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573653</v>
+        <v>573634</v>
       </c>
       <c r="R4" t="n">
-        <v>7056943</v>
+        <v>7056989</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD4" t="b">

--- a/artfynd/A 55422-2024 artfynd.xlsx
+++ b/artfynd/A 55422-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123805063</v>
+        <v>123802394</v>
       </c>
       <c r="B2" t="n">
-        <v>91032</v>
+        <v>91012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573734</v>
+        <v>573646</v>
       </c>
       <c r="R2" t="n">
-        <v>7056784</v>
+        <v>7056941</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123802574</v>
+        <v>123802294</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
+        <v>91299</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573619</v>
+        <v>573643</v>
       </c>
       <c r="R3" t="n">
-        <v>7056981</v>
+        <v>7056933</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123802394</v>
+        <v>123802574</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>79891</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,21 +915,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573646</v>
+        <v>573619</v>
       </c>
       <c r="R4" t="n">
-        <v>7056941</v>
+        <v>7056981</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123802226</v>
+        <v>123801614</v>
       </c>
       <c r="B6" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,34 +1144,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bergmyran, Bergmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>573653</v>
+        <v>573694</v>
       </c>
       <c r="R6" t="n">
-        <v>7056943</v>
+        <v>7056860</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123801614</v>
+        <v>123805063</v>
       </c>
       <c r="B7" t="n">
-        <v>56714</v>
+        <v>91032</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1256,39 +1261,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>5442</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bergmyran, Bergmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>573694</v>
+        <v>573734</v>
       </c>
       <c r="R7" t="n">
-        <v>7056860</v>
+        <v>7056784</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1357,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123802294</v>
+        <v>123802226</v>
       </c>
       <c r="B8" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,21 +1373,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1397,10 +1397,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>573643</v>
+        <v>573653</v>
       </c>
       <c r="R8" t="n">
-        <v>7056933</v>
+        <v>7056943</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 55422-2024 artfynd.xlsx
+++ b/artfynd/A 55422-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123802394</v>
+        <v>123802226</v>
       </c>
       <c r="B2" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573646</v>
+        <v>573653</v>
       </c>
       <c r="R2" t="n">
-        <v>7056941</v>
+        <v>7056943</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123802294</v>
+        <v>123802574</v>
       </c>
       <c r="B3" t="n">
-        <v>91299</v>
+        <v>79891</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573643</v>
+        <v>573619</v>
       </c>
       <c r="R3" t="n">
-        <v>7056933</v>
+        <v>7056981</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123802574</v>
+        <v>123802645</v>
       </c>
       <c r="B4" t="n">
-        <v>79891</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,34 +915,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bergmyran, Bergmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573619</v>
+        <v>573634</v>
       </c>
       <c r="R4" t="n">
-        <v>7056981</v>
+        <v>7056989</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123802645</v>
+        <v>123805063</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>91032</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,39 +1032,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bergmyran, Bergmyran, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>573634</v>
+        <v>573734</v>
       </c>
       <c r="R5" t="n">
-        <v>7056989</v>
+        <v>7056784</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123801614</v>
+        <v>123802394</v>
       </c>
       <c r="B6" t="n">
-        <v>56714</v>
+        <v>91012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1144,39 +1144,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Bergmyran, Bergmyran, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>573694</v>
+        <v>573646</v>
       </c>
       <c r="R6" t="n">
-        <v>7056860</v>
+        <v>7056941</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1203,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1213,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1240,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123805063</v>
+        <v>123802294</v>
       </c>
       <c r="B7" t="n">
-        <v>91032</v>
+        <v>91299</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,21 +1256,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1285,10 +1280,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>573734</v>
+        <v>573643</v>
       </c>
       <c r="R7" t="n">
-        <v>7056784</v>
+        <v>7056933</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1320,7 +1315,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1330,7 +1325,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1357,10 +1352,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>123802226</v>
+        <v>123801614</v>
       </c>
       <c r="B8" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1373,34 +1368,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bergmyran, Bergmyran, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>573653</v>
+        <v>573694</v>
       </c>
       <c r="R8" t="n">
-        <v>7056943</v>
+        <v>7056860</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 55422-2024 artfynd.xlsx
+++ b/artfynd/A 55422-2024 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123802226</v>
+        <v>123802294</v>
       </c>
       <c r="B2" t="n">
-        <v>78810</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>573653</v>
+        <v>573643</v>
       </c>
       <c r="R2" t="n">
-        <v>7056943</v>
+        <v>7056933</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123802574</v>
+        <v>123802394</v>
       </c>
       <c r="B3" t="n">
-        <v>79891</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>573619</v>
+        <v>573646</v>
       </c>
       <c r="R3" t="n">
-        <v>7056981</v>
+        <v>7056941</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,15 +889,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>123802645</v>
+        <v>123805063</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -915,39 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Bergmyran, Bergmyran, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>573634</v>
+        <v>573734</v>
       </c>
       <c r="R4" t="n">
-        <v>7056989</v>
+        <v>7056784</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:48</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1016,37 +996,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>123805063</v>
+        <v>123802226</v>
       </c>
       <c r="B5" t="n">
-        <v>91032</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1056,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>573734</v>
+        <v>573653</v>
       </c>
       <c r="R5" t="n">
-        <v>7056784</v>
+        <v>7056943</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:48</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,15 +1103,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>123802394</v>
+        <v>123802574</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1144,21 +1114,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1168,10 +1138,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>573646</v>
+        <v>573619</v>
       </c>
       <c r="R6" t="n">
-        <v>7056941</v>
+        <v>7056981</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,7 +1173,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,7 +1183,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1240,50 +1210,50 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>123802294</v>
+        <v>123802645</v>
       </c>
       <c r="B7" t="n">
-        <v>91299</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bergmyran, Bergmyran, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>573643</v>
+        <v>573634</v>
       </c>
       <c r="R7" t="n">
-        <v>7056933</v>
+        <v>7056989</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1315,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1325,7 +1295,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,16 +1325,11 @@
         <v>123801614</v>
       </c>
       <c r="B8" t="n">
-        <v>56714</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57132</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">

--- a/artfynd/A 55422-2024 artfynd.xlsx
+++ b/artfynd/A 55422-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123802294</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123802394</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123805063</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123802226</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1207,6 +1232,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123802574</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1319,6 +1349,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123802645</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1431,8 +1466,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123801614</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>